--- a/DataSources/BudgetPivot.xlsx
+++ b/DataSources/BudgetPivot.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\virve\Documents\Sales Report\Data Sources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bcsk-my.sharepoint.com/personal/virve_rani_bcs_ee/Documents/Documents/andmetarkus2026/DataSources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCAE10B5-45A0-45B6-9425-907757C8EB34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{DCAE10B5-45A0-45B6-9425-907757C8EB34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A585F4A-28B7-4A77-9D09-7BC2F6B180F3}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A448E068-D00D-4D43-BCF5-A1C382574009}"/>
   </bookViews>
@@ -453,7 +453,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="9.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:73" x14ac:dyDescent="0.35">
@@ -1355,6 +1355,14 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="761d0801-ebf0-405d-ba89-5fd93677c3c3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100D8BC7FD0AA6EEA499D9B093AC6E3EACC" ma:contentTypeVersion="9" ma:contentTypeDescription="Loo uus dokument" ma:contentTypeScope="" ma:versionID="411f39168d3a60f88cab6123ec507e65">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="761d0801-ebf0-405d-ba89-5fd93677c3c3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a27d5aba181a0c08311b137ab24f3109" ns3:_="">
     <xsd:import namespace="761d0801-ebf0-405d-ba89-5fd93677c3c3"/>
@@ -1528,14 +1536,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="761d0801-ebf0-405d-ba89-5fd93677c3c3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FBE3A50-6F1A-440E-B3F5-0B26957AC0AF}">
   <ds:schemaRefs>
@@ -1545,6 +1545,22 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A884E914-1D52-465C-BAB9-37C7C7FD6F6C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="761d0801-ebf0-405d-ba89-5fd93677c3c3"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F257E011-7AA5-473B-9963-C74D274B0489}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1560,20 +1576,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A884E914-1D52-465C-BAB9-37C7C7FD6F6C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="761d0801-ebf0-405d-ba89-5fd93677c3c3"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>